--- a/step_1_calibration_and_identificationn/helpers/calibration/calibration.xlsx
+++ b/step_1_calibration_and_identificationn/helpers/calibration/calibration.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BOWN1111PC1\Documents\Mohamed\IsolatorSetup_gaurav\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BOWN1111PC1\Documents\Mohamed\ColumnSetup_gaurav\step_1_calibration_and_identificationn\helpers\calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ECEE52-D6AA-444F-878F-4528E2BC989E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4BB617-9552-4643-95E5-5DCB643CDE80}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5556" xr2:uid="{DC8E32BD-E2AE-45DE-8E94-D61150AD8363}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>MTS</t>
   </si>
@@ -43,6 +43,21 @@
   </si>
   <si>
     <t>v2d</t>
+  </si>
+  <si>
+    <t>MTS abs</t>
+  </si>
+  <si>
+    <t>MTS rel</t>
+  </si>
+  <si>
+    <t>speedgoat</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>kips to N</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F398B50C-7D42-4BCB-93C8-5526FAA41667}">
-  <dimension ref="B2:F21"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="1"/>
@@ -1653,6 +1668,27 @@
         <v>7.6219512195121943</v>
       </c>
     </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
